--- a/PTBR/Lang/PTBR/Dialog/dialog.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/dialog.xlsx
@@ -373,7 +373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.11" customWidth="1" style="13" min="1" max="1"/>
@@ -2272,6 +2272,170 @@
       <c r="D88" s="17" t="inlineStr">
         <is>
           <t>I'm so happy, #pc! I'm truly happy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="74.59999999999999" customHeight="1" s="14">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>rob1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Eu te subestimei!
+Por favor, pare com isso!
+Você vai se arrepender de ter vindo atrás de mim.
+O que te faz pensar que um bandido comum pode me enfrentar?
+Por favor, pare. Você vai se arrepender.
+Mercenários, afastem esse malandro.
+Hmph. Você não vê quantos guardas eu tenho?</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>見損なった{よ}！
+ひどい{よ}、やめて{くれ}！
+返り討ちにしてくれる{よ}。
+ごろつき風情に何ができるという{のだ}？
+やめて{くれ}。きっと後悔する{よ}。
+傭兵さんたち、このごろつきを追い払って{くれ}。
+ふん、この護衛の数が見えないの{か}？</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>I misjudged you!
+Please, stop this!
+You'll regret coming after me.
+What makes you think a common thug can take me on?
+Please stop. You'll regret this.
+Mercenaries, drive this ruffian off.
+Hmph. Can't you see how many guards I have?</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32.8" customHeight="1" s="14">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>mama_yes</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>A mamãe está aqui!
+Sim, eu sou sua mamãe!
+A mamãe está bem aqui.</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>ママだよ！
+{はい}、ママ{だ}～！
+ママはここにいる{のだ}。</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Mommy's here!
+Yes, I'm your mommy!
+Mommy is right here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="64.15000000000001" customHeight="1" s="14">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>mama_no</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Xô, xô!
+Eu não sou sua mãe!
+Do que você está falando...?
+Que pena... você bateu com a cabeça?
+Isso é assustador...
+Huh...?</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>シッシッ！
+ママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+気持ち悪い{よ}…
+え…？</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shoo, shoo!
+I'm not your mom!
+What are you talking about...?
+How pitiful... did you hit your head?
+That’s creepy...
+Huh...? </t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32.8" customHeight="1" s="14">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>baby_yes</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mamãe!
+...Você é minha... mamãe?
+Mãe... mamãe...?</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>ママー！
+私の…ママなの{か}？
+マ…ママ…？</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Mommy!
+...You are my...mommy?
+Ma... mama...?</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="43.25" customHeight="1" s="14">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>baby_no</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Você não é minha mamãe!
+Do que você está falando...?
+Que pena... você bateu com a cabeça?
+Huh...?</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>こんなのママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+え…？</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You're not my mommy!
+What are you talking about...?
+How pitiful... did you hit your head?
+Huh...? </t>
         </is>
       </c>
     </row>

--- a/PTBR/Lang/PTBR/Dialog/dialog.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/dialog.xlsx
@@ -373,7 +373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.11" customWidth="1" style="13" min="1" max="1"/>
@@ -2272,170 +2272,6 @@
       <c r="D88" s="17" t="inlineStr">
         <is>
           <t>I'm so happy, #pc! I'm truly happy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="74.59999999999999" customHeight="1" s="14">
-      <c r="A89" s="13" t="inlineStr">
-        <is>
-          <t>rob1</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Eu te subestimei!
-Por favor, pare com isso!
-Você vai se arrepender de ter vindo atrás de mim.
-O que te faz pensar que um bandido comum pode me enfrentar?
-Por favor, pare. Você vai se arrepender.
-Mercenários, afastem esse malandro.
-Hmph. Você não vê quantos guardas eu tenho?</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="inlineStr">
-        <is>
-          <t>見損なった{よ}！
-ひどい{よ}、やめて{くれ}！
-返り討ちにしてくれる{よ}。
-ごろつき風情に何ができるという{のだ}？
-やめて{くれ}。きっと後悔する{よ}。
-傭兵さんたち、このごろつきを追い払って{くれ}。
-ふん、この護衛の数が見えないの{か}？</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>I misjudged you!
-Please, stop this!
-You'll regret coming after me.
-What makes you think a common thug can take me on?
-Please stop. You'll regret this.
-Mercenaries, drive this ruffian off.
-Hmph. Can't you see how many guards I have?</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="32.8" customHeight="1" s="14">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>mama_yes</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>A mamãe está aqui!
-Sim, eu sou sua mamãe!
-A mamãe está bem aqui.</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="inlineStr">
-        <is>
-          <t>ママだよ！
-{はい}、ママ{だ}～！
-ママはここにいる{のだ}。</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>Mommy's here!
-Yes, I'm your mommy!
-Mommy is right here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="64.15000000000001" customHeight="1" s="14">
-      <c r="A91" s="13" t="inlineStr">
-        <is>
-          <t>mama_no</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Xô, xô!
-Eu não sou sua mãe!
-Do que você está falando...?
-Que pena... você bateu com a cabeça?
-Isso é assustador...
-Huh...?</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr">
-        <is>
-          <t>シッシッ！
-ママじゃない{よ}！
-君は何を言っている{のだ}？
-かわいそうに…頭を打ったの{か}？
-気持ち悪い{よ}…
-え…？</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shoo, shoo!
-I'm not your mom!
-What are you talking about...?
-How pitiful... did you hit your head?
-That’s creepy...
-Huh...? </t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="32.8" customHeight="1" s="14">
-      <c r="A92" s="13" t="inlineStr">
-        <is>
-          <t>baby_yes</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Mamãe!
-...Você é minha... mamãe?
-Mãe... mamãe...?</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>ママー！
-私の…ママなの{か}？
-マ…ママ…？</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Mommy!
-...You are my...mommy?
-Ma... mama...?</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="43.25" customHeight="1" s="14">
-      <c r="A93" s="13" t="inlineStr">
-        <is>
-          <t>baby_no</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Você não é minha mamãe!
-Do que você está falando...?
-Que pena... você bateu com a cabeça?
-Huh...?</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr">
-        <is>
-          <t>こんなのママじゃない{よ}！
-君は何を言っている{のだ}？
-かわいそうに…頭を打ったの{か}？
-え…？</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You're not my mommy!
-What are you talking about...?
-How pitiful... did you hit your head?
-Huh...? </t>
         </is>
       </c>
     </row>
